--- a/Home_SOC_Inventory.xlsx
+++ b/Home_SOC_Inventory.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b19c7f844800b906/Desktop/Home SOC Inventory/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b19c7f844800b906/Desktop/Cyber Security Portfolio/Home Lab Inventory/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{F4813237-BE4C-41C7-943C-7256E61C4A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8B8A88B-0082-4257-BD29-B66CD46C6C81}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1949B66-92E3-401F-9C19-4B577320F2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47895" yWindow="7740" windowWidth="19410" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32430" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SOC Inventory" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="78">
   <si>
     <t>Asset ID</t>
   </si>
@@ -71,6 +71,12 @@
     <t>Windows</t>
   </si>
   <si>
+    <t>192.168.1.165</t>
+  </si>
+  <si>
+    <t>30-89-4A-61-3B-72</t>
+  </si>
+  <si>
     <t>Home Office</t>
   </si>
   <si>
@@ -98,6 +104,15 @@
     <t>Virtual Machine</t>
   </si>
   <si>
+    <t>Ubuntu</t>
+  </si>
+  <si>
+    <t>192.168.0.32</t>
+  </si>
+  <si>
+    <t>08:00:27:30:80:F8</t>
+  </si>
+  <si>
     <t>VMware/VirtualBox</t>
   </si>
   <si>
@@ -107,7 +122,7 @@
     <t>Critical</t>
   </si>
   <si>
-    <t>SIEM Manager</t>
+    <t>Wazuh Manager - Updated after TP-Link migration</t>
   </si>
   <si>
     <t>ASSET-003</t>
@@ -122,6 +137,9 @@
     <t>macOS</t>
   </si>
   <si>
+    <t>192.168.1.173</t>
+  </si>
+  <si>
     <t>Home</t>
   </si>
   <si>
@@ -134,6 +152,75 @@
     <t>macOS endpoint monitored by Wazuh</t>
   </si>
   <si>
+    <t>ASSET-004</t>
+  </si>
+  <si>
+    <t>TP-Link</t>
+  </si>
+  <si>
+    <t>Router</t>
+  </si>
+  <si>
+    <t>Router OS</t>
+  </si>
+  <si>
+    <t>192.168.1.1</t>
+  </si>
+  <si>
+    <t>68-7F-F0-76-FA-E2</t>
+  </si>
+  <si>
+    <t>ASSET- 005</t>
+  </si>
+  <si>
+    <t>Kali-VM</t>
+  </si>
+  <si>
+    <t>Kali Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0.2.15 </t>
+  </si>
+  <si>
+    <t>08:00:27:8a:35:d2</t>
+  </si>
+  <si>
+    <t>Ip= VirtualBox NAT Address</t>
+  </si>
+  <si>
+    <t>ASSET-006</t>
+  </si>
+  <si>
+    <t>TP-Link Tether</t>
+  </si>
+  <si>
+    <t>Management Application</t>
+  </si>
+  <si>
+    <t>iOS</t>
+  </si>
+  <si>
+    <t>Matthew Mohler</t>
+  </si>
+  <si>
+    <t>Router administration and monitoring</t>
+  </si>
+  <si>
+    <t>ASSET-007</t>
+  </si>
+  <si>
+    <t>GitHub Portfolio</t>
+  </si>
+  <si>
+    <t>Documentation Platform</t>
+  </si>
+  <si>
+    <t>Web</t>
+  </si>
+  <si>
+    <t>Home SOC project documentation repository</t>
+  </si>
+  <si>
     <t>Priority</t>
   </si>
   <si>
@@ -164,58 +251,10 @@
     <t>Create custom alert rules</t>
   </si>
   <si>
-    <t>ASSET-004</t>
-  </si>
-  <si>
-    <t>Verizon Router</t>
-  </si>
-  <si>
-    <t>Router</t>
-  </si>
-  <si>
-    <t>Router OS</t>
-  </si>
-  <si>
-    <t>ASSET- 005</t>
-  </si>
-  <si>
-    <t>Kali-VM</t>
-  </si>
-  <si>
-    <t>Kali Linux</t>
-  </si>
-  <si>
-    <t>192.168.1.242</t>
-  </si>
-  <si>
-    <t>192.168.1.165</t>
-  </si>
-  <si>
-    <t>30-89-4A-61-3B-72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0.2.15 </t>
-  </si>
-  <si>
-    <t>08:00:27:8a:35:d2</t>
-  </si>
-  <si>
-    <t>192.168.1.1</t>
-  </si>
-  <si>
-    <t>ac-91-9b-10-53-77</t>
-  </si>
-  <si>
-    <t>08:00:27:30:80:F8</t>
-  </si>
-  <si>
-    <t>Ip= VirtualBox NAT Address</t>
-  </si>
-  <si>
-    <t>Ubuntu</t>
-  </si>
-  <si>
-    <t>192.168.1.173</t>
+    <t>Create DHCP reservations for Wazuh and Kali</t>
+  </si>
+  <si>
+    <t>Prevent IP changes after router upgrades</t>
   </si>
 </sst>
 </file>
@@ -256,14 +295,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -280,18 +364,18 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SOCInventoryTable" displayName="SOCInventoryTable" ref="A1:L6">
   <autoFilter ref="A1:L6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Asset ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Device Name"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Device Type"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Operating System"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="IP Address"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="MAC Address"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Location"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Owner/User"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Wazuh Agent Installed"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Monitoring Status"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Criticality"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Notes"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Asset ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Device Name" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Device Type" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Operating System" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="IP Address" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="MAC Address" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Location" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Owner/User" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Wazuh Agent Installed" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Monitoring Status" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Criticality" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Notes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -582,229 +666,289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="35" customWidth="1"/>
+    <col min="1" max="1" width="14" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18" style="3" customWidth="1"/>
+    <col min="5" max="5" width="16" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20" style="3" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14" style="3" customWidth="1"/>
+    <col min="12" max="12" width="35" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="C7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="K7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>62</v>
+      <c r="J8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -817,7 +961,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="40" customWidth="1"/>
@@ -825,13 +969,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>11</v>
@@ -839,57 +983,71 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
